--- a/data/trans_dic/P16A12-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P16A12-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para la diabetes en las dos últimas semanas</t>
+          <t>Población que ha consumido medicinas para la diabetes en las dos últimas semanas (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,42; 7,03</t>
+          <t>2,4; 7,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,01; 10,25</t>
+          <t>3,86; 9,93</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,07; 9,76</t>
+          <t>4,17; 10,24</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,23; 13,37</t>
+          <t>7,02; 13,57</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,96; 6,77</t>
+          <t>2,22; 7,22</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,04; 10,13</t>
+          <t>3,76; 9,82</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,84; 6,24</t>
+          <t>1,83; 6,38</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,47; 9,67</t>
+          <t>5,52; 9,76</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,84; 6,39</t>
+          <t>2,74; 6,2</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4,74; 9,14</t>
+          <t>4,63; 8,98</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,47; 7,24</t>
+          <t>3,48; 7,13</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6,87; 10,62</t>
+          <t>7,03; 10,73</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,65; 7,99</t>
+          <t>3,67; 7,68</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,87; 9,7</t>
+          <t>4,89; 9,78</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,81; 9,4</t>
+          <t>4,83; 9,33</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,53; 9,11</t>
+          <t>4,45; 9,25</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,95; 10,85</t>
+          <t>6,01; 10,6</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,52; 14,12</t>
+          <t>8,51; 14,05</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,1; 13,82</t>
+          <t>7,83; 13,23</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,92; 9,64</t>
+          <t>5,94; 9,93</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,18; 8,41</t>
+          <t>5,29; 8,49</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,35; 11,17</t>
+          <t>7,13; 10,82</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6,94; 10,72</t>
+          <t>6,88; 10,57</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,83; 8,75</t>
+          <t>5,76; 8,78</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,98; 7,89</t>
+          <t>2,77; 7,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,83; 14,23</t>
+          <t>7,1; 14,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,55; 6,69</t>
+          <t>2,43; 6,87</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8,68; 14,4</t>
+          <t>8,76; 14,44</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,93; 10,39</t>
+          <t>4,8; 10,3</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,1; 14,35</t>
+          <t>7,4; 14,35</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,96; 9,82</t>
+          <t>3,91; 9,52</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,01; 12,97</t>
+          <t>7,95; 12,92</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,34; 8,19</t>
+          <t>4,52; 8,29</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8,27; 13,05</t>
+          <t>8,09; 12,87</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,83; 7,51</t>
+          <t>3,64; 7,16</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9,1; 12,92</t>
+          <t>8,91; 12,68</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,11; 7,62</t>
+          <t>3,38; 7,91</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,75; 8,87</t>
+          <t>3,92; 8,61</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,35; 16,37</t>
+          <t>9,1; 16,18</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,19; 11,79</t>
+          <t>6,13; 11,93</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,02; 7,46</t>
+          <t>3,07; 7,21</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,65; 11,22</t>
+          <t>5,9; 11,48</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,41; 9,56</t>
+          <t>4,4; 9,75</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,31; 7,54</t>
+          <t>3,29; 7,45</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,66; 6,64</t>
+          <t>3,64; 6,4</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5,35; 9,22</t>
+          <t>5,43; 9,0</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,49; 11,92</t>
+          <t>7,4; 11,7</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,77; 8,38</t>
+          <t>4,76; 8,63</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,55; 7,9</t>
+          <t>2,55; 7,88</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,35; 13,6</t>
+          <t>5,35; 13,99</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,61; 10,31</t>
+          <t>3,41; 9,88</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,17; 13,88</t>
+          <t>7,37; 14,77</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,14; 13,46</t>
+          <t>5,13; 13,48</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,86; 17,01</t>
+          <t>7,92; 16,91</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,27; 13,92</t>
+          <t>6,24; 13,79</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>9,53; 15,02</t>
+          <t>9,44; 15,2</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,54; 9,53</t>
+          <t>4,43; 9,65</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7,67; 13,6</t>
+          <t>7,72; 13,99</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5,67; 10,62</t>
+          <t>5,62; 10,88</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,33; 13,55</t>
+          <t>9,23; 13,58</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,28; 8,95</t>
+          <t>3,34; 9,38</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,41; 10,25</t>
+          <t>4,18; 10,12</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,02; 9,79</t>
+          <t>4,17; 10,38</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11,4; 17,83</t>
+          <t>11,43; 18,18</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,84; 6,27</t>
+          <t>1,52; 6,18</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7,17; 14,61</t>
+          <t>7,47; 15,21</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,87; 10,48</t>
+          <t>3,97; 10,72</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8,17; 13,08</t>
+          <t>8,38; 13,5</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,93; 6,44</t>
+          <t>3,17; 6,99</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6,46; 11,08</t>
+          <t>6,61; 11,18</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4,74; 9,28</t>
+          <t>4,66; 9,38</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>10,6; 14,67</t>
+          <t>10,36; 14,39</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,92; 8,92</t>
+          <t>4,94; 9,2</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,11; 10,54</t>
+          <t>6,09; 10,56</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8,47; 13,88</t>
+          <t>8,51; 13,39</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,23; 10,37</t>
+          <t>6,23; 10,38</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,65; 8,56</t>
+          <t>4,64; 8,39</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,27; 10,55</t>
+          <t>6,33; 10,55</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,92; 10,11</t>
+          <t>5,8; 10,52</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,04; 6,01</t>
+          <t>1,94; 6,09</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,33; 8,03</t>
+          <t>5,41; 8,07</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6,62; 9,63</t>
+          <t>6,79; 9,86</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7,73; 11,19</t>
+          <t>7,79; 11,19</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,75; 7,35</t>
+          <t>3,79; 7,43</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,34; 7,7</t>
+          <t>4,54; 7,81</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4,6; 8,21</t>
+          <t>4,62; 8,42</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7,14; 11,15</t>
+          <t>7,04; 11,03</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,13; 7,41</t>
+          <t>2,25; 7,51</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,06; 7,52</t>
+          <t>4,06; 7,41</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,04; 7,35</t>
+          <t>4,13; 7,43</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,78; 11,07</t>
+          <t>6,87; 11,15</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>4,84; 7,41</t>
+          <t>4,79; 7,33</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4,65; 7,02</t>
+          <t>4,55; 6,98</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4,76; 7,22</t>
+          <t>4,68; 7,28</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7,36; 10,47</t>
+          <t>7,55; 10,29</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>3,36; 6,76</t>
+          <t>3,2; 6,79</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4,85; 6,39</t>
+          <t>4,86; 6,4</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6,41; 8,27</t>
+          <t>6,46; 8,31</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7,46; 9,33</t>
+          <t>7,45; 9,32</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6,44; 9,24</t>
+          <t>6,12; 9,24</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5,26; 7,02</t>
+          <t>5,29; 6,93</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,59; 9,45</t>
+          <t>7,52; 9,4</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,94; 8,84</t>
+          <t>6,98; 8,92</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>5,55; 7,66</t>
+          <t>5,68; 7,71</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5,24; 6,38</t>
+          <t>5,3; 6,41</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7,21; 8,6</t>
+          <t>7,22; 8,5</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7,46; 8,77</t>
+          <t>7,46; 8,79</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>6,61; 8,28</t>
+          <t>6,48; 8,24</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para la diabetes en las dos últimas semanas</t>
+          <t>Población que ha consumido medicinas para la diabetes en las dos últimas semanas (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6620; 19204</t>
+          <t>6558; 19227</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>11727; 29953</t>
+          <t>11279; 29007</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11963; 28680</t>
+          <t>12262; 30087</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>22525; 41628</t>
+          <t>21866; 42255</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>5125; 17671</t>
+          <t>5780; 18826</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11373; 28506</t>
+          <t>10567; 27634</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5306; 18020</t>
+          <t>5285; 18431</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>15845; 27993</t>
+          <t>16000; 28265</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>15149; 34103</t>
+          <t>14640; 33082</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>27164; 52431</t>
+          <t>26537; 51484</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>20238; 42188</t>
+          <t>20242; 41542</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>41306; 63817</t>
+          <t>42281; 64488</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17983; 39399</t>
+          <t>18089; 37881</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>24634; 49046</t>
+          <t>24720; 49423</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>24185; 47247</t>
+          <t>24262; 46878</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>23418; 47115</t>
+          <t>23003; 47874</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>29962; 54669</t>
+          <t>30265; 53438</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>44553; 73786</t>
+          <t>44509; 73445</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>42365; 72297</t>
+          <t>40965; 69188</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>30410; 49516</t>
+          <t>30497; 51015</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>51653; 83861</t>
+          <t>52787; 84619</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>75545; 114816</t>
+          <t>73342; 111273</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>71193; 109963</t>
+          <t>70542; 108391</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>60161; 90234</t>
+          <t>59377; 90494</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>9512; 25166</t>
+          <t>8822; 24865</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>22073; 45981</t>
+          <t>22934; 45727</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8139; 21309</t>
+          <t>7734; 21880</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>27419; 45498</t>
+          <t>27676; 45641</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>16549; 34864</t>
+          <t>16112; 34557</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>24214; 48953</t>
+          <t>25238; 48920</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13305; 33038</t>
+          <t>13141; 32022</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>27968; 45281</t>
+          <t>27765; 45093</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>28377; 53560</t>
+          <t>29557; 54243</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>54913; 86660</t>
+          <t>53752; 85480</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>25065; 49211</t>
+          <t>23837; 46919</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>60563; 85972</t>
+          <t>59258; 84367</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11140; 27329</t>
+          <t>12135; 28363</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>14007; 33165</t>
+          <t>14643; 32189</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>34586; 60561</t>
+          <t>33665; 59861</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>19347; 36856</t>
+          <t>19148; 37296</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11235; 27720</t>
+          <t>11421; 26797</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>21916; 43537</t>
+          <t>22894; 44521</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>17062; 37035</t>
+          <t>17029; 37766</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>15750; 35863</t>
+          <t>15674; 35424</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>26730; 48449</t>
+          <t>26547; 46697</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>40794; 70258</t>
+          <t>41389; 68609</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>56681; 90240</t>
+          <t>56023; 88601</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>37596; 66024</t>
+          <t>37552; 68006</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>5192; 16070</t>
+          <t>5186; 16017</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>11376; 28926</t>
+          <t>11367; 29745</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7628; 21777</t>
+          <t>7202; 20868</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12820; 24812</t>
+          <t>13174; 26400</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>10680; 27958</t>
+          <t>10653; 28002</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>17267; 37346</t>
+          <t>17390; 37135</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13708; 30417</t>
+          <t>13636; 30139</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>19884; 31345</t>
+          <t>19697; 31721</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>18669; 39153</t>
+          <t>18197; 39672</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>33140; 58779</t>
+          <t>33378; 60465</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>24360; 45661</t>
+          <t>24168; 46784</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>36163; 52497</t>
+          <t>35748; 52613</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>8890; 24229</t>
+          <t>9033; 25392</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>12082; 28091</t>
+          <t>11440; 27724</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>10576; 25768</t>
+          <t>10978; 27308</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>30741; 48063</t>
+          <t>30823; 49022</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5106; 17437</t>
+          <t>4231; 17201</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>20024; 40791</t>
+          <t>20845; 42445</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10560; 28618</t>
+          <t>10842; 29291</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>20994; 33619</t>
+          <t>21545; 34697</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>16098; 35358</t>
+          <t>17378; 38371</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>35722; 61275</t>
+          <t>36549; 61848</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>25405; 49775</t>
+          <t>24994; 50274</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>55846; 77244</t>
+          <t>54586; 75767</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>30265; 54839</t>
+          <t>30354; 56598</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>40479; 69868</t>
+          <t>40389; 69984</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>55588; 91110</t>
+          <t>55902; 87908</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>38909; 64723</t>
+          <t>38891; 64798</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>29655; 54619</t>
+          <t>29605; 53536</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>43522; 73221</t>
+          <t>43888; 73182</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>40946; 69877</t>
+          <t>40092; 72752</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>17320; 51013</t>
+          <t>16488; 51691</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>66785; 100646</t>
+          <t>67743; 101199</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>89874; 130696</t>
+          <t>92134; 133766</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>104249; 150812</t>
+          <t>105031; 150830</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>55232; 108317</t>
+          <t>55857; 109464</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>32209; 57167</t>
+          <t>33737; 58014</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>35711; 63823</t>
+          <t>35868; 65397</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>55618; 86808</t>
+          <t>54798; 85879</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>19822; 68854</t>
+          <t>20882; 69786</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>31778; 58941</t>
+          <t>31801; 58037</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>33153; 60403</t>
+          <t>33906; 61020</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>56049; 91430</t>
+          <t>56765; 92131</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>34568; 52996</t>
+          <t>34267; 52406</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>71041; 107119</t>
+          <t>69412; 106490</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>76110; 115413</t>
+          <t>74855; 116372</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>118067; 167963</t>
+          <t>121106; 165098</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>55288; 111144</t>
+          <t>52625; 111620</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>158970; 209442</t>
+          <t>159289; 209717</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>219446; 282832</t>
+          <t>221138; 284347</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>253157; 316850</t>
+          <t>252972; 316276</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>222751; 319679</t>
+          <t>211549; 319523</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>177613; 237097</t>
+          <t>178922; 234057</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>269319; 335355</t>
+          <t>266721; 333511</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>246106; 313433</t>
+          <t>247421; 316075</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>203062; 280081</t>
+          <t>207611; 281874</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>349023; 424353</t>
+          <t>352733; 426803</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>502682; 599412</t>
+          <t>502880; 592595</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>517317; 608821</t>
+          <t>517427; 610129</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>470477; 588927</t>
+          <t>461231; 586496</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16A12-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P16A12-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,66%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,4; 7,04</t>
+          <t>2,37; 7,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,86; 9,93</t>
+          <t>3,98; 10,29</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,17; 10,24</t>
+          <t>3,98; 10,36</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,02; 13,57</t>
+          <t>7,05; 13,19</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,22; 7,22</t>
+          <t>2,01; 7,18</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,76; 9,82</t>
+          <t>4,23; 10,15</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,83; 6,38</t>
+          <t>1,74; 6,28</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,52; 9,76</t>
+          <t>5,66; 9,66</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,74; 6,2</t>
+          <t>2,65; 6,16</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4,63; 8,98</t>
+          <t>4,42; 8,87</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,48; 7,13</t>
+          <t>3,59; 7,37</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,03; 10,73</t>
+          <t>6,9; 10,62</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,06%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,67; 7,68</t>
+          <t>3,57; 7,82</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,89; 9,78</t>
+          <t>4,66; 9,38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,83; 9,33</t>
+          <t>4,92; 9,36</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,45; 9,25</t>
+          <t>4,44; 8,84</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,01; 10,6</t>
+          <t>5,71; 10,51</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,51; 14,05</t>
+          <t>8,3; 13,82</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,83; 13,23</t>
+          <t>7,67; 13,22</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,94; 9,93</t>
+          <t>5,81; 9,46</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,29; 8,49</t>
+          <t>5,18; 8,44</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,13; 10,82</t>
+          <t>7,3; 11,01</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6,88; 10,57</t>
+          <t>6,94; 10,59</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,76; 8,78</t>
+          <t>5,86; 8,63</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,67%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,77; 7,8</t>
+          <t>2,97; 7,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,1; 14,15</t>
+          <t>7,25; 14,28</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,43; 6,87</t>
+          <t>2,7; 6,71</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8,76; 14,44</t>
+          <t>8,67; 14,36</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,8; 10,3</t>
+          <t>4,85; 10,61</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,4; 14,35</t>
+          <t>7,3; 14,38</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,91; 9,52</t>
+          <t>3,93; 9,43</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,95; 12,92</t>
+          <t>8,09; 12,76</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,52; 8,29</t>
+          <t>4,66; 8,14</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8,09; 12,87</t>
+          <t>8,18; 12,97</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,64; 7,16</t>
+          <t>3,77; 7,26</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8,91; 12,68</t>
+          <t>8,91; 12,56</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>7,42%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,38; 7,91</t>
+          <t>3,09; 7,66</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,92; 8,61</t>
+          <t>3,84; 8,64</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,1; 16,18</t>
+          <t>9,03; 15,78</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,13; 11,93</t>
+          <t>6,09; 11,63</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,07; 7,21</t>
+          <t>3,02; 7,13</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,9; 11,48</t>
+          <t>5,71; 11,24</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,4; 9,75</t>
+          <t>4,55; 9,65</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,29; 7,45</t>
+          <t>4,95; 8,41</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,64; 6,4</t>
+          <t>3,54; 6,69</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5,43; 9,0</t>
+          <t>5,33; 9,16</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,4; 11,7</t>
+          <t>7,62; 11,96</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,76; 8,63</t>
+          <t>6,02; 9,26</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>10,56%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,55; 7,88</t>
+          <t>2,58; 8,4</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,35; 13,99</t>
+          <t>5,21; 13,38</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,41; 9,88</t>
+          <t>3,43; 9,87</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,37; 14,77</t>
+          <t>6,52; 12,76</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,13; 13,48</t>
+          <t>5,14; 13,67</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,92; 16,91</t>
+          <t>7,93; 16,68</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,24; 13,79</t>
+          <t>5,94; 13,71</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>9,44; 15,2</t>
+          <t>9,22; 14,44</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,43; 9,65</t>
+          <t>4,65; 9,59</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7,72; 13,99</t>
+          <t>7,67; 13,52</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5,62; 10,88</t>
+          <t>5,41; 10,51</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,23; 13,58</t>
+          <t>8,48; 12,71</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,45%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,34; 9,38</t>
+          <t>3,27; 9,22</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,18; 10,12</t>
+          <t>4,1; 10,3</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,17; 10,38</t>
+          <t>4,23; 9,88</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11,43; 18,18</t>
+          <t>11,41; 17,57</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,52; 6,18</t>
+          <t>1,52; 6,13</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7,47; 15,21</t>
+          <t>7,18; 14,87</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,97; 10,72</t>
+          <t>3,81; 10,63</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8,38; 13,5</t>
+          <t>8,19; 13,34</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3,17; 6,99</t>
+          <t>2,84; 6,59</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6,61; 11,18</t>
+          <t>6,26; 11,34</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4,66; 9,38</t>
+          <t>4,63; 8,86</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>10,36; 14,39</t>
+          <t>10,53; 14,44</t>
         </is>
       </c>
     </row>
@@ -1504,19 +1504,19 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
+          <t>8,68%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>6,43%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
           <t>8,14%</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>6,43%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>8,14%</t>
-        </is>
-      </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
           <t>7,88%</t>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>7,15%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,94; 9,2</t>
+          <t>5,17; 9,09</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,09; 10,56</t>
+          <t>6,18; 10,52</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8,51; 13,39</t>
+          <t>8,37; 13,36</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,23; 10,38</t>
+          <t>6,64; 10,67</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,64; 8,39</t>
+          <t>4,69; 8,57</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,33; 10,55</t>
+          <t>6,23; 10,35</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,8; 10,52</t>
+          <t>5,8; 10,35</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,94; 6,09</t>
+          <t>4,46; 7,29</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,41; 8,07</t>
+          <t>5,29; 7,93</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6,79; 9,86</t>
+          <t>6,75; 9,73</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7,79; 11,19</t>
+          <t>7,79; 11,13</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,79; 7,43</t>
+          <t>5,98; 8,41</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>6,32%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,54; 7,81</t>
+          <t>4,34; 7,8</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4,62; 8,42</t>
+          <t>4,55; 8,24</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7,04; 11,03</t>
+          <t>7,24; 10,94</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,25; 7,51</t>
+          <t>5,07; 8,32</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,06; 7,41</t>
+          <t>4,04; 7,49</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,13; 7,43</t>
+          <t>3,97; 7,19</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,87; 11,15</t>
+          <t>6,93; 11,24</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>4,79; 7,33</t>
+          <t>4,72; 7,5</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4,55; 6,98</t>
+          <t>4,69; 7,01</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4,68; 7,28</t>
+          <t>4,81; 7,18</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7,55; 10,29</t>
+          <t>7,52; 10,36</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>3,2; 6,79</t>
+          <t>5,34; 7,47</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>8,03%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4,86; 6,4</t>
+          <t>4,83; 6,4</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6,46; 8,31</t>
+          <t>6,37; 8,25</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7,45; 9,32</t>
+          <t>7,44; 9,24</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6,12; 9,24</t>
+          <t>7,86; 9,61</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5,29; 6,93</t>
+          <t>5,24; 6,85</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,52; 9,4</t>
+          <t>7,53; 9,37</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,98; 8,92</t>
+          <t>6,92; 8,9</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>5,68; 7,71</t>
+          <t>6,83; 8,16</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5,3; 6,41</t>
+          <t>5,3; 6,44</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7,22; 8,5</t>
+          <t>7,27; 8,57</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7,46; 8,79</t>
+          <t>7,46; 8,73</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>6,48; 8,24</t>
+          <t>7,51; 8,6</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>30724</t>
+          <t>31244</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>21291</t>
+          <t>23730</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>52016</t>
+          <t>54974</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6558; 19227</t>
+          <t>6483; 19317</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>11279; 29007</t>
+          <t>11632; 30052</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12262; 30087</t>
+          <t>11685; 30438</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>21866; 42255</t>
+          <t>22484; 42063</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>5780; 18826</t>
+          <t>5245; 18731</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10567; 27634</t>
+          <t>11903; 28543</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5285; 18431</t>
+          <t>5028; 18118</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>16000; 28265</t>
+          <t>17874; 30539</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>14640; 33082</t>
+          <t>14122; 32883</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>26537; 51484</t>
+          <t>25347; 50872</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>20242; 41542</t>
+          <t>20924; 42952</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>42281; 64488</t>
+          <t>43794; 67449</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>34421</t>
+          <t>34725</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>39507</t>
+          <t>41174</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>73929</t>
+          <t>75898</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18089; 37881</t>
+          <t>17621; 38582</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>24720; 49423</t>
+          <t>23535; 47435</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>24262; 46878</t>
+          <t>24729; 47042</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>23003; 47874</t>
+          <t>23515; 46841</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>30265; 53438</t>
+          <t>28782; 52964</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>44509; 73445</t>
+          <t>43398; 72227</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>40965; 69188</t>
+          <t>40119; 69146</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>30497; 51015</t>
+          <t>31680; 51557</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>52787; 84619</t>
+          <t>51644; 84142</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>73342; 111273</t>
+          <t>75051; 113257</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>70542; 108391</t>
+          <t>71225; 108626</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>59377; 90494</t>
+          <t>62957; 92766</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>35790</t>
+          <t>35403</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>36002</t>
+          <t>36330</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>71792</t>
+          <t>71733</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>8822; 24865</t>
+          <t>9474; 23596</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>22934; 45727</t>
+          <t>23423; 46137</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7734; 21880</t>
+          <t>8611; 21373</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>27676; 45641</t>
+          <t>27389; 45362</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>16112; 34557</t>
+          <t>16279; 35585</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>25238; 48920</t>
+          <t>24893; 49032</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13141; 32022</t>
+          <t>13220; 31704</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>27765; 45093</t>
+          <t>28841; 45476</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>29557; 54243</t>
+          <t>30479; 53237</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>53752; 85480</t>
+          <t>54347; 86144</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>23837; 46919</t>
+          <t>24658; 47533</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>59258; 84367</t>
+          <t>59886; 84419</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>26774</t>
+          <t>31804</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>25724</t>
+          <t>27229</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>52498</t>
+          <t>59033</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>12135; 28363</t>
+          <t>11084; 27471</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>14643; 32189</t>
+          <t>14360; 32301</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>33665; 59861</t>
+          <t>33393; 58371</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>19148; 37296</t>
+          <t>22723; 43391</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11421; 26797</t>
+          <t>11233; 26489</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>22894; 44521</t>
+          <t>22169; 43595</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>17029; 37766</t>
+          <t>17630; 37382</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>15674; 35424</t>
+          <t>20904; 35473</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>26547; 46697</t>
+          <t>25817; 48846</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>41389; 68609</t>
+          <t>40605; 69827</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>56023; 88601</t>
+          <t>57702; 90541</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>37552; 68006</t>
+          <t>47902; 73612</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18245</t>
+          <t>19245</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>25384</t>
+          <t>26456</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>43629</t>
+          <t>45701</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>5186; 16017</t>
+          <t>5251; 17074</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>11367; 29745</t>
+          <t>11067; 28455</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7202; 20868</t>
+          <t>7250; 20838</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>13174; 26400</t>
+          <t>13401; 26242</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>10653; 28002</t>
+          <t>10671; 28393</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>17390; 37135</t>
+          <t>17403; 36624</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13636; 30139</t>
+          <t>12978; 29968</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>19697; 31721</t>
+          <t>20947; 32803</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>18197; 39672</t>
+          <t>19126; 39424</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>33378; 60465</t>
+          <t>33164; 58440</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>24168; 46784</t>
+          <t>23257; 45160</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>35748; 52613</t>
+          <t>36729; 55021</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>38642</t>
+          <t>38821</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>27066</t>
+          <t>27727</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>65709</t>
+          <t>66548</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>9033; 25392</t>
+          <t>8864; 24980</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>11440; 27724</t>
+          <t>11223; 28222</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>10978; 27308</t>
+          <t>11136; 25993</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>30823; 49022</t>
+          <t>30882; 47567</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4231; 17201</t>
+          <t>4225; 17056</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>20845; 42445</t>
+          <t>20042; 41514</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10842; 29291</t>
+          <t>10406; 29025</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>21545; 34697</t>
+          <t>21589; 35189</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>17378; 38371</t>
+          <t>15576; 36198</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>36549; 61848</t>
+          <t>34634; 62743</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>24994; 50274</t>
+          <t>24809; 47532</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>54586; 75767</t>
+          <t>56283; 77193</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>50799</t>
+          <t>62489</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>35959</t>
+          <t>44203</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>86759</t>
+          <t>106692</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>30354; 56598</t>
+          <t>31771; 55884</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>40389; 69984</t>
+          <t>40957; 69748</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>55902; 87908</t>
+          <t>54963; 87734</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>38891; 64798</t>
+          <t>47753; 76799</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>29605; 53536</t>
+          <t>29955; 54665</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>43888; 73182</t>
+          <t>43195; 71826</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>40092; 72752</t>
+          <t>40116; 71544</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>16488; 51691</t>
+          <t>34415; 56262</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>67743; 101199</t>
+          <t>66243; 99336</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>92134; 133766</t>
+          <t>91612; 131988</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>105031; 150830</t>
+          <t>104977; 150029</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>55857; 109464</t>
+          <t>89207; 125382</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>46712</t>
+          <t>52426</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>42783</t>
+          <t>50398</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>89495</t>
+          <t>102824</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>33737; 58014</t>
+          <t>32234; 57925</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>35868; 65397</t>
+          <t>35385; 64008</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>54798; 85879</t>
+          <t>56364; 85202</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>20882; 69786</t>
+          <t>40457; 66392</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>31801; 58037</t>
+          <t>31630; 58656</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>33906; 61020</t>
+          <t>32615; 59078</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>56765; 92131</t>
+          <t>57239; 92834</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>34267; 52406</t>
+          <t>39137; 62275</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>69412; 106490</t>
+          <t>71531; 107045</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>74855; 116372</t>
+          <t>76836; 114732</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>121106; 165098</t>
+          <t>120597; 166231</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>52625; 111620</t>
+          <t>86988; 121565</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>282108</t>
+          <t>306157</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>253717</t>
+          <t>277246</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>535825</t>
+          <t>583403</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>159289; 209717</t>
+          <t>158228; 209691</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>221138; 284347</t>
+          <t>218039; 282352</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>252972; 316276</t>
+          <t>252521; 313703</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>211549; 319523</t>
+          <t>277521; 339357</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>178922; 234057</t>
+          <t>177006; 231537</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>266721; 333511</t>
+          <t>267237; 332385</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>247421; 316075</t>
+          <t>245451; 315598</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>207611; 281874</t>
+          <t>254897; 304505</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>352733; 426803</t>
+          <t>352579; 428694</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>502880; 592595</t>
+          <t>506456; 597037</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>517427; 610129</t>
+          <t>517451; 605904</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>461231; 586496</t>
+          <t>545388; 624473</t>
         </is>
       </c>
     </row>
